--- a/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-genotyping.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-genotyping.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -383,7 +383,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -809,7 +809,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -838,7 +838,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -924,7 +924,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1100,7 +1100,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1145,7 +1145,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1168,7 +1168,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1519,7 +1519,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1548,7 +1548,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1607,7 +1607,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1678,7 +1678,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1758,7 +1758,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1808,7 +1808,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1841,7 +1841,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1900,7 +1900,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1985,7 +1985,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2035,7 +2035,7 @@
     <t>Observation.component.value[x]:valueCodeableConcept</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.0}
 </t>
   </si>
   <si>

--- a/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-genotyping.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-genotyping.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-genotyping.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-genotyping.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}eu-lab-1:If observation status is other then "registered" or "cancelled", at least one of these Observation elements shall be provided:  "value", "dataAbsentReason", "hasMember" or "component" {(status in ('registered'|'cancelled')) or value.exists() or hasMember.exists() or component.exists() or dataAbsentReason.exists()}eu-lab-2:If observation has components and observation status is other then "registered" or "cancelled", at least one of these Observation.component elements shall be provided:  "value" or "dataAbsentReason" {component.exists() implies (status in ('registered'|'cancelled')) or component.value.exists() or component.dataAbsentReason.exists()}ch-elm-expecting-specimen-specification:If Observation.code is a member of http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-expecting-specimen-specification, then Specimen.type must be a member of the mapped ValueSet in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-expecting-specimen-specification-to-results-completion-vs {code.memberOf('http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-expecting-specimen-specification') implies (specimen.resolve().exists() and specimen.resolve().type.exists() and specimen.resolve().type.memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-expecting-specimen-specification-to-results-completion-vs'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code))}ch-elm-patient-name-representation-initial-loinc:If Observation.code is mapped to initials in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient.name.first and given must have one character and the following elements must not be provided: patient.telecom, patient.address.line {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code = 'initials' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientInitials')))}ch-elm-patient-name-representation-initial-snomedct:If Observation.code is mapped to initials in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient.name.first and given must have one character and the following elements must not be provided: patient.telecom, patient.address.line {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code = 'initials' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientInitials')))}ch-elm-patient-name-representation-initial-or-vctcode-loinc:If Observation.code is mapped to initials or vctcode in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient.name family and given must have one character or - in case of a VCT patient - must be masked and the following elements must not be provided: patient.telecom, patient.address.line. {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code = 'initials-or-vctcode' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientInitials') or subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientVCT')))}ch-elm-patient-name-representation-initial-or-vctcode-snomedct:If Observation.code is mapped to initials or vctcode in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient.name family and given must have one character or - in case of a VCT patient - must be masked and the following elements must not be provided: patient.telecom, patient.address.line. {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code = 'initials-or-vctcode' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientInitials') or subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientVCT')))}ch-elm-patient-name-representation-hiv-code-loinc:If Observation.code is mapped to hiv-code in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient representation must follow profile resource profile: CH ELM Patient HIV {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code = 'hiv-code' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientHIV')))}ch-elm-patient-name-representation-hiv-code-snomedct:If Observation.code is mapped to hiv-code in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient representation must follow profile resource profile: CH ELM Patient HIV {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code = 'hiv-code' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientHIV')))}ch-elm-component-code-geno-loinc:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code, then the component.code code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).exists() implies component.code.all(memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code))}ch-elm-component-code-geno-snomedct:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code, then the component.code code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).exists() implies component.code.all(memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code))}ch-elm-component-interpretation-code-geno-loinc:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code, then the component.interpretation code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).exists() implies component.interpretation.all(memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code))}ch-elm-component-interpretation-code-geno-snomedct:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code, then the component.interpretation code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).exists() implies component.interpretation.all(memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code))}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}eu-lab-1:If observation status is other then "registered" or "cancelled", at least one of these Observation elements shall be provided:  "value", "dataAbsentReason", "hasMember" or "component" {(status in ('registered'|'cancelled')) or value.exists() or hasMember.exists() or component.exists() or dataAbsentReason.exists()}eu-lab-2:If observation has components and observation status is other then "registered" or "cancelled", at least one of these Observation.component elements shall be provided:  "value" or "dataAbsentReason" {component.exists() implies (status in ('registered'|'cancelled')) or component.value.exists() or component.dataAbsentReason.exists()}ch-elm-expecting-specimen-specification:If Observation.code is a member of http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-expecting-specimen-specification, then Specimen.type must be a member of the mapped ValueSet in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-expecting-specimen-specification-to-results-completion-vs {code.memberOf('http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-expecting-specimen-specification') implies (specimen.resolve().exists() and specimen.resolve().type.exists() and specimen.resolve().type.memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-expecting-specimen-specification-to-results-completion-vs'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code))}ch-elm-patient-name-representation-initial-loinc:If Observation.code is mapped to initials in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient.name.first and given must have one character and the following elements must not be provided: patient.telecom, patient.address.line {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code = 'initials' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientInitials')))}ch-elm-patient-name-representation-initial-snomedct:If Observation.code is mapped to initials in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient.name.first and given must have one character and the following elements must not be provided: patient.telecom, patient.address.line {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code = 'initials' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientInitials')))}ch-elm-patient-name-representation-initial-or-vctcode-loinc:If Observation.code is mapped to initials or vctcode in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient.name family and given must have one character or - in case of a VCT patient - must be masked and the following elements must not be provided: patient.telecom, patient.address.line. {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code = 'initials-or-vctcode' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientInitials') or subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientVCT')))}ch-elm-patient-name-representation-initial-or-vctcode-snomedct:If Observation.code is mapped to initials or vctcode in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient.name family and given must have one character or - in case of a VCT patient - must be masked and the following elements must not be provided: patient.telecom, patient.address.line. {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code = 'initials-or-vctcode' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientInitials') or subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientVCT')))}ch-elm-patient-name-representation-hiv-code-loinc:If Observation.code is mapped to hiv-code in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient representation must follow profile resource profile: CH ELM Patient HIV {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code = 'hiv-code' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientHIV')))}ch-elm-patient-name-representation-hiv-code-snomedct:If Observation.code is mapped to hiv-code in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation then patient representation must follow profile resource profile: CH ELM Patient HIV {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).empty() or ('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-to-foph-patient-name-representation'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code = 'hiv-code' implies (subject.resolve().conformsTo('http://fhir.ch/ig/ch-elm/StructureDefinition/ChElmPatientHIV')))}ch-elm-component-code-geno-loinc:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code, then the component.code code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).exists() implies component.code.all(memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code))}ch-elm-component-code-geno-snomedct:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code, then the component.code code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).exists() implies component.code.all(memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-code'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code))}ch-elm-component-interpretation-code-geno-loinc:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code, then the component.interpretation code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).exists() implies component.interpretation.all(memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code))}ch-elm-component-interpretation-code-geno-snomedct:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code, then the component.interpretation code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).exists() implies component.interpretation.all(memberOf('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-interpretation-code'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code))}ch-elm-component-observation-profile-geno-loinc:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-observation-profile, then the observation must be conform to the mapped profile for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-susc-to-component-observation-profile'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).exists() implies conformsTo('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-observation-profile'.resolve().group.where(source='http://loinc.org').element.where(code=%context.code.coding.where(system='http://loinc.org').first().code).target.first().code)}ch-elm-component-observation-profile-geno-snomedct:If Observation.code is mapped in http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-observation-profile, then the component.code code must be a member of the mapped ValueSet for genotyping testing {'http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-observation-profile'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).exists() implies conformsTo('http://fhir.ch/ig/ch-elm/ConceptMap/ch-elm-results-geno-to-component-observation-profile'.resolve().group.where(source='http://snomed.info/sct').element.where(code=%context.code.coding.where(system='http://snomed.info/sct').first().code).target.first().code)}</t>
   </si>
   <si>
     <t>Event</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-genotyping.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-observation-results-laboratory-genotyping.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
